--- a/src/dataset_berlabel_final.xlsx
+++ b/src/dataset_berlabel_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Temporary Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\kuliah\NetCheckPCR\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85CD093-EC7E-4E94-8959-F7D02A8714DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset Bersih" sheetId="1" r:id="rId1"/>
@@ -1027,7 +1027,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1042,7 +1042,7 @@
     <col min="11" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>31</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
         <v>42</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>49</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>52</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
         <v>56</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>58</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
         <v>60</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>62</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
         <v>64</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>67</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>69</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>73</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>76</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>78</v>
       </c>
@@ -1742,7 +1742,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>81</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>82</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>83</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>85</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>86</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>87</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
         <v>88</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>89</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>90</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>92</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
         <v>94</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="4" t="s">
         <v>98</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="4" t="s">
         <v>76</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>102</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="4" t="s">
         <v>103</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>104</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="4" t="s">
         <v>105</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
         <v>107</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="4" t="s">
         <v>109</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
         <v>111</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="4" t="s">
         <v>112</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
         <v>114</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="4" t="s">
         <v>116</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
         <v>117</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="4" t="s">
         <v>118</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>119</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="4" t="s">
         <v>120</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
         <v>121</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
         <v>122</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
         <v>123</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
         <v>125</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>127</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" s="4" t="s">
         <v>129</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
         <v>130</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" s="4" t="s">
         <v>131</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
         <v>132</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" s="4" t="s">
         <v>134</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
         <v>135</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" s="4" t="s">
         <v>136</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
         <v>137</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" s="4" t="s">
         <v>138</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
         <v>139</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" s="4" t="s">
         <v>140</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
         <v>141</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" s="4" t="s">
         <v>143</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
         <v>144</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" s="4" t="s">
         <v>145</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>146</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70" s="4" t="s">
         <v>147</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>148</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72" s="4" t="s">
         <v>149</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
         <v>150</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A74" s="4" t="s">
         <v>151</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
         <v>153</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A76" s="4" t="s">
         <v>155</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
         <v>156</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A78" s="4" t="s">
         <v>157</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
         <v>160</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A80" s="4" t="s">
         <v>161</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
         <v>162</v>
       </c>
@@ -3877,7 +3877,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A82" s="4" t="s">
         <v>163</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
         <v>164</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A84" s="4" t="s">
         <v>165</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>168</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A86" s="4" t="s">
         <v>169</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
         <v>170</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A88" s="4" t="s">
         <v>171</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
         <v>173</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A90" s="4" t="s">
         <v>174</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
         <v>176</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A92" s="4" t="s">
         <v>177</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
         <v>178</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A94" s="4" t="s">
         <v>179</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
         <v>180</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A96" s="4" t="s">
         <v>181</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
         <v>182</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A98" s="4" t="s">
         <v>183</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
         <v>185</v>
       </c>
@@ -4507,7 +4507,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A100" s="4" t="s">
         <v>187</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
         <v>188</v>
       </c>
